--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484130_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484130_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.676399999999999</v>
+        <v>8.685</v>
       </c>
       <c r="E2" t="n">
-        <v>6.563</v>
+        <v>5.6277</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1134</v>
+        <v>3.0573</v>
       </c>
       <c r="G2" t="n">
         <v>4.534</v>
@@ -610,13 +610,13 @@
         <v>2.579</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0315</v>
+        <v>1.0401</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4966</v>
+        <v>0.5613</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5349</v>
+        <v>0.4788</v>
       </c>
       <c r="V2" t="n">
         <v>0.532</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8846</v>
+        <v>5.652</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3603</v>
+        <v>3.7911</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5243</v>
+        <v>1.8609</v>
       </c>
       <c r="G3" t="n">
         <v>2.7464</v>
@@ -688,13 +688,13 @@
         <v>2.3806</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6201</v>
+        <v>0.1474</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.442</v>
+        <v>-0.0112</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1781</v>
+        <v>0.1586</v>
       </c>
       <c r="V3" t="n">
         <v>3.3534</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MARTIN MONZON</t>
+          <t>L. MARTINEZ YRANZO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2444</v>
+        <v>3.7675</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7346</v>
+        <v>2.1933</v>
       </c>
       <c r="F4" t="n">
-        <v>3.5098</v>
+        <v>1.5743</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7915</v>
+        <v>2.4837</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.6754</v>
+        <v>0.6906</v>
       </c>
       <c r="I4" t="n">
-        <v>3.4669</v>
+        <v>1.7931</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4609</v>
+        <v>3.0495</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.0343</v>
+        <v>1.684</v>
       </c>
       <c r="L4" t="n">
-        <v>2.4951</v>
+        <v>1.3655</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3307</v>
+        <v>-0.5658</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6411</v>
+        <v>-0.9933999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9718</v>
+        <v>0.4276</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5871</v>
+        <v>0.7935</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R4" t="n">
-        <v>2.579</v>
+        <v>1.7855</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5286</v>
+        <v>0.4903</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.544</v>
+        <v>-0.1303</v>
       </c>
       <c r="U4" t="n">
-        <v>2.0726</v>
+        <v>0.6206</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3373</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.8097</v>
+        <v>0.266</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.4724</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. MARTINEZ YRANZO</t>
+          <t>J. MARTIN MONZON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9043</v>
+        <v>3.6638</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7228</v>
+        <v>1.0237</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1815</v>
+        <v>2.6401</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4837</v>
+        <v>0.7915</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6906</v>
+        <v>-2.6754</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7931</v>
+        <v>3.4669</v>
       </c>
       <c r="J5" t="n">
-        <v>3.0495</v>
+        <v>0.4609</v>
       </c>
       <c r="K5" t="n">
-        <v>1.684</v>
+        <v>-2.0343</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3655</v>
+        <v>2.4951</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5658</v>
+        <v>0.3307</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9933999999999999</v>
+        <v>-0.6411</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4276</v>
+        <v>0.9718</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7935</v>
+        <v>1.5871</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7855</v>
+        <v>2.579</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.373</v>
+        <v>0.9479</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6008</v>
+        <v>-0.2549</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2278</v>
+        <v>1.2029</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.3373</v>
       </c>
       <c r="W5" t="n">
-        <v>0.266</v>
+        <v>1.8097</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.266</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4538</v>
+        <v>2.5901</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6828</v>
+        <v>0.8472</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7709</v>
+        <v>1.7429</v>
       </c>
       <c r="G6" t="n">
         <v>0.1664</v>
@@ -922,13 +922,13 @@
         <v>1.7855</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0301</v>
+        <v>0.1063</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.306</v>
+        <v>-0.1416</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2759</v>
+        <v>0.2479</v>
       </c>
       <c r="V6" t="n">
         <v>0.532</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2637</v>
+        <v>0.1796</v>
       </c>
       <c r="E7" t="n">
         <v>-0.1247</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3884</v>
+        <v>0.3043</v>
       </c>
       <c r="G7" t="n">
         <v>0.2065</v>
@@ -1000,13 +1000,13 @@
         <v>0.1984</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1412</v>
+        <v>-0.2253</v>
       </c>
       <c r="T7" t="n">
         <v>-0.1247</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0165</v>
+        <v>-0.1006</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0891</v>
+        <v>-0.061</v>
       </c>
       <c r="E8" t="n">
         <v>-0.0422</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0469</v>
+        <v>-0.0188</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0454</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0436</v>
+        <v>-0.0156</v>
       </c>
       <c r="T8" t="n">
         <v>-0.0623</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1562</v>
+        <v>-0.1755</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6965</v>
+        <v>0.4528</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8527</v>
+        <v>-0.6282</v>
       </c>
       <c r="G9" t="n">
         <v>0.3872</v>
@@ -1156,13 +1156,13 @@
         <v>0.7935</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2017</v>
+        <v>-0.221</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1928</v>
+        <v>-0.051</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3945</v>
+        <v>-0.1701</v>
       </c>
       <c r="V9" t="n">
         <v>-1.1352</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6389</v>
+        <v>-0.9479</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3671</v>
+        <v>-1.7322</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7282</v>
+        <v>0.7843</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3386</v>
@@ -1234,13 +1234,13 @@
         <v>1.1903</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4987</v>
+        <v>-0.8077</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9352</v>
+        <v>-0.3003</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5635</v>
+        <v>-0.5074</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0766</v>
+        <v>-2.0868</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7022</v>
+        <v>-0.6002</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3744</v>
+        <v>-1.4866</v>
       </c>
       <c r="G11" t="n">
         <v>-0.835</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0352</v>
+        <v>-0.0454</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0623</v>
+        <v>0.0397</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0272</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2065</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. NDIAYE</t>
+          <t>J. ROSA DE SOUSA DA SILVA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6182</v>
+        <v>-2.6014</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5144</v>
+        <v>-3.3104</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1038</v>
+        <v>0.709</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.1541</v>
+        <v>-0.8698</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.3303</v>
+        <v>-0.2674</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1762</v>
+        <v>-0.6024</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3525</v>
+        <v>-0.091</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3926</v>
+        <v>0.3884</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0402</v>
+        <v>-0.4794</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8016</v>
+        <v>-0.7788</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9376</v>
+        <v>-0.6558</v>
       </c>
       <c r="O12" t="n">
-        <v>0.136</v>
+        <v>-0.123</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.7935</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9919</v>
+        <v>-2.9758</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1984</v>
+        <v>1.3887</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2698</v>
+        <v>-0.1446</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5044999999999999</v>
+        <v>-0.2437</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2347</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9405</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.6745</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. ROSA DE SOUSA DA SILVA</t>
+          <t>L. NDIAYE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.0883</v>
+        <v>-2.9702</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.7412</v>
+        <v>-1.9225</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6529</v>
+        <v>-1.0477</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.8698</v>
+        <v>-1.1541</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2674</v>
+        <v>-1.3303</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6024</v>
+        <v>0.1762</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.091</v>
+        <v>-0.3525</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3884</v>
+        <v>-0.3926</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.4794</v>
+        <v>0.0402</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.7788</v>
+        <v>-0.8016</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6558</v>
+        <v>-0.9376</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.123</v>
+        <v>0.136</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.5871</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.9758</v>
+        <v>-0.9919</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3887</v>
+        <v>0.1984</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6314</v>
+        <v>-0.0822</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6744</v>
+        <v>0.0964</v>
       </c>
       <c r="U13" t="n">
-        <v>0.043</v>
+        <v>-0.1786</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.9405</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>14.7599</v>
+        <v>15.6952</v>
       </c>
       <c r="E14" t="n">
-        <v>5.268199999999999</v>
+        <v>6.203599999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>9.491600000000002</v>
+        <v>9.4918</v>
       </c>
       <c r="G14" t="n">
         <v>8.072800000000003</v>
@@ -1516,7 +1516,7 @@
         <v>0.6556000000000002</v>
       </c>
       <c r="I14" t="n">
-        <v>7.4172</v>
+        <v>7.417199999999999</v>
       </c>
       <c r="J14" t="n">
         <v>10.395</v>
@@ -1546,13 +1546,13 @@
         <v>14.8789</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2549000000000003</v>
+        <v>1.1902</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.5578</v>
+        <v>-0.6225999999999998</v>
       </c>
       <c r="U14" t="n">
-        <v>1.8128</v>
+        <v>1.813</v>
       </c>
       <c r="V14" t="n">
         <v>1.4725</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.0417</v>
+        <v>6.1837</v>
       </c>
       <c r="E15" t="n">
-        <v>5.3983</v>
+        <v>5.2963</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6434</v>
+        <v>0.8874</v>
       </c>
       <c r="G15" t="n">
         <v>6.8285</v>
@@ -1624,13 +1624,13 @@
         <v>1.7855</v>
       </c>
       <c r="S15" t="n">
-        <v>0.242</v>
+        <v>0.384</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1135</v>
+        <v>0.0115</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1285</v>
+        <v>0.3726</v>
       </c>
       <c r="V15" t="n">
         <v>1.3518</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.1824</v>
+        <v>2.4461</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7995</v>
+        <v>0.9833</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3829</v>
+        <v>1.4628</v>
       </c>
       <c r="G16" t="n">
         <v>1.0262</v>
@@ -1702,13 +1702,13 @@
         <v>1.1903</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9659</v>
+        <v>0.2296</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8616</v>
+        <v>0.0454</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1042</v>
+        <v>0.1842</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.7565</v>
+        <v>1.2983</v>
       </c>
       <c r="E17" t="n">
-        <v>4.3572</v>
+        <v>2.6227</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.6007</v>
+        <v>-1.3243</v>
       </c>
       <c r="G17" t="n">
         <v>1.6948</v>
@@ -1780,13 +1780,13 @@
         <v>0.3968</v>
       </c>
       <c r="S17" t="n">
-        <v>2.2418</v>
+        <v>0.7837</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2788</v>
+        <v>0.5443</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0369</v>
+        <v>0.2394</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3866</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0081</v>
+        <v>0.2121</v>
       </c>
       <c r="E18" t="n">
         <v>-0.1266</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1185</v>
+        <v>0.3387</v>
       </c>
       <c r="G18" t="n">
         <v>-0.06419999999999999</v>
@@ -1858,13 +1858,13 @@
         <v>0.3968</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3407</v>
+        <v>-0.1205</v>
       </c>
       <c r="T18" t="n">
         <v>-0.187</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1536</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4092</v>
+        <v>-1.2332</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2351</v>
+        <v>-2.031</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8259</v>
+        <v>0.7978</v>
       </c>
       <c r="G19" t="n">
         <v>-0.06419999999999999</v>
@@ -1936,13 +1936,13 @@
         <v>0.5952</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0436</v>
+        <v>0.2196</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3117</v>
+        <v>-0.1077</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3554</v>
+        <v>0.3273</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. MONTALVO PEREZ</t>
+          <t>P. SANTIAGO PAZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2661</v>
+        <v>-1.7336</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8658</v>
+        <v>-1.619</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4003</v>
+        <v>-0.1146</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1148</v>
+        <v>-0.3293</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2623</v>
+        <v>-2.1923</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8524</v>
+        <v>1.863</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1966</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.277</v>
+        <v>-0.6038</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0803</v>
+        <v>1.1698</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9181</v>
+        <v>-0.8953</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0147</v>
+        <v>-1.5885</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9328</v>
+        <v>0.6932</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3968</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9919</v>
+        <v>-1.1903</v>
       </c>
       <c r="R20" t="n">
         <v>0.5952</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1859</v>
+        <v>-0.4719</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0567</v>
+        <v>-0.6574</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1292</v>
+        <v>0.1855</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9405</v>
+        <v>-0.3373</v>
       </c>
       <c r="W20" t="n">
-        <v>0.266</v>
+        <v>-0.3373</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. SANTIAGO PAZ</t>
+          <t>A. MONTALVO PEREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.668</v>
+        <v>-2.4463</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3332</v>
+        <v>-1.0699</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3348</v>
+        <v>-1.3764</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3293</v>
+        <v>-1.1148</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.1923</v>
+        <v>-0.2623</v>
       </c>
       <c r="I21" t="n">
-        <v>1.863</v>
+        <v>-0.8524</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5659999999999999</v>
+        <v>-0.1966</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6038</v>
+        <v>-0.277</v>
       </c>
       <c r="L21" t="n">
-        <v>1.1698</v>
+        <v>0.0803</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8953</v>
+        <v>-0.9181</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.5885</v>
+        <v>0.0147</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6932</v>
+        <v>-0.9328</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.5952</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1903</v>
+        <v>-0.9919</v>
       </c>
       <c r="R21" t="n">
         <v>0.5952</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4063</v>
+        <v>0.0057</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3716</v>
+        <v>-0.1473</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0347</v>
+        <v>0.153</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3373</v>
+        <v>-0.9405</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3373</v>
+        <v>0.266</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3507</v>
+        <v>-2.8686</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2386</v>
+        <v>-2.7285</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1121</v>
+        <v>-0.1402</v>
       </c>
       <c r="G22" t="n">
         <v>-1.9203</v>
@@ -2170,13 +2170,13 @@
         <v>0.9919</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3135</v>
+        <v>0.1686</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4364</v>
+        <v>0.0737</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1229</v>
+        <v>0.0949</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9186</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5742</v>
+        <v>-2.9739</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.9724</v>
+        <v>-2.5643</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6017</v>
+        <v>-0.4096</v>
       </c>
       <c r="G23" t="n">
         <v>-4.1667</v>
@@ -2248,13 +2248,13 @@
         <v>0.3968</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7448</v>
+        <v>-0.1445</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0599</v>
+        <v>-0.6518</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3151</v>
+        <v>0.5072</v>
       </c>
       <c r="V23" t="n">
         <v>0.9405</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.7995</v>
+        <v>-3.4194</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.117</v>
+        <v>-1.7089</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6825</v>
+        <v>-1.7106</v>
       </c>
       <c r="G24" t="n">
         <v>-2.2444</v>
@@ -2326,13 +2326,13 @@
         <v>1.3887</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3157</v>
+        <v>0.6958</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.255</v>
+        <v>0.1531</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5707</v>
+        <v>0.5426</v>
       </c>
       <c r="V24" t="n">
         <v>-2.2676</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.4101</v>
+        <v>-3.928</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.6052</v>
+        <v>-3.0951</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8048</v>
+        <v>-0.8329</v>
       </c>
       <c r="G25" t="n">
         <v>-3.3363</v>
@@ -2404,13 +2404,13 @@
         <v>0.5952</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0106</v>
+        <v>-0.5285</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.4874</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0131</v>
+        <v>-0.0412</v>
       </c>
       <c r="V25" t="n">
         <v>0.532</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.2547</v>
+        <v>-4.9367</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.5527</v>
+        <v>-3.4506</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.702</v>
+        <v>-1.4861</v>
       </c>
       <c r="G26" t="n">
         <v>-4.3825</v>
@@ -2482,13 +2482,13 @@
         <v>0.9919</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.4342</v>
+        <v>-0.1162</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5044</v>
+        <v>-0.4023</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0702</v>
+        <v>0.2862</v>
       </c>
       <c r="V26" t="n">
         <v>0.5538999999999999</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-14.76</v>
+        <v>-13.3995</v>
       </c>
       <c r="E27" t="n">
-        <v>-9.491599999999998</v>
+        <v>-9.4916</v>
       </c>
       <c r="F27" t="n">
-        <v>-5.2682</v>
+        <v>-3.908</v>
       </c>
       <c r="G27" t="n">
         <v>-8.0732</v>
@@ -2560,13 +2560,13 @@
         <v>9.919499999999999</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.2552000000000001</v>
+        <v>1.1054</v>
       </c>
       <c r="T27" t="n">
         <v>-1.8129</v>
       </c>
       <c r="U27" t="n">
-        <v>1.5579</v>
+        <v>2.9183</v>
       </c>
       <c r="V27" t="n">
         <v>-1.4724</v>
